--- a/analysis/data/annotation/[Archived] Labeling SDG 6 - Benchmarking Dataset.xlsx
+++ b/analysis/data/annotation/[Archived] Labeling SDG 6 - Benchmarking Dataset.xlsx
@@ -18691,7 +18691,7 @@
     <row r="2">
       <c r="A2" s="19" t="str">
         <f t="shared" ref="A2:A86" si="1">LEFT(MD5(B2), 7)</f>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B2" s="12" t="s">
         <v>164</v>
@@ -18713,7 +18713,7 @@
     <row r="3">
       <c r="A3" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>153</v>
@@ -18738,7 +18738,7 @@
     <row r="4">
       <c r="A4" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B4" s="48" t="s">
         <v>473</v>
@@ -18763,7 +18763,7 @@
     <row r="5">
       <c r="A5" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B5" s="12" t="s">
         <v>256</v>
@@ -18788,7 +18788,7 @@
     <row r="6">
       <c r="A6" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B6" s="12" t="s">
         <v>75</v>
@@ -18813,7 +18813,7 @@
     <row r="7">
       <c r="A7" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B7" s="12" t="s">
         <v>199</v>
@@ -18838,7 +18838,7 @@
     <row r="8">
       <c r="A8" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B8" s="12" t="s">
         <v>218</v>
@@ -18860,7 +18860,7 @@
     <row r="9">
       <c r="A9" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B9" s="48" t="s">
         <v>475</v>
@@ -18885,7 +18885,7 @@
     <row r="10">
       <c r="A10" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B10" s="12" t="s">
         <v>162</v>
@@ -18907,7 +18907,7 @@
     <row r="11">
       <c r="A11" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B11" s="12" t="s">
         <v>250</v>
@@ -18929,7 +18929,7 @@
     <row r="12">
       <c r="A12" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B12" s="12" t="s">
         <v>133</v>
@@ -18951,7 +18951,7 @@
     <row r="13">
       <c r="A13" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B13" s="12" t="s">
         <v>180</v>
@@ -18973,7 +18973,7 @@
     <row r="14">
       <c r="A14" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B14" s="12" t="s">
         <v>264</v>
@@ -18995,7 +18995,7 @@
     <row r="15">
       <c r="A15" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B15" s="12" t="s">
         <v>208</v>
@@ -19017,7 +19017,7 @@
     <row r="16">
       <c r="A16" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B16" s="12" t="s">
         <v>143</v>
@@ -19039,7 +19039,7 @@
     <row r="17">
       <c r="A17" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B17" s="12" t="s">
         <v>266</v>
@@ -19064,7 +19064,7 @@
     <row r="18">
       <c r="A18" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B18" s="12" t="s">
         <v>222</v>
@@ -19086,7 +19086,7 @@
     <row r="19">
       <c r="A19" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B19" s="12" t="s">
         <v>94</v>
@@ -19108,7 +19108,7 @@
     <row r="20">
       <c r="A20" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B20" s="48" t="s">
         <v>477</v>
@@ -19133,7 +19133,7 @@
     <row r="21">
       <c r="A21" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B21" s="12" t="s">
         <v>139</v>
@@ -19155,7 +19155,7 @@
     <row r="22">
       <c r="A22" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>254</v>
@@ -19177,7 +19177,7 @@
     <row r="23">
       <c r="A23" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B23" s="48" t="s">
         <v>478</v>
@@ -19202,7 +19202,7 @@
     <row r="24">
       <c r="A24" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>197</v>
@@ -19224,7 +19224,7 @@
     <row r="25">
       <c r="A25" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B25" s="12" t="s">
         <v>90</v>
@@ -19246,7 +19246,7 @@
     <row r="26">
       <c r="A26" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B26" s="12" t="s">
         <v>96</v>
@@ -19268,7 +19268,7 @@
     <row r="27">
       <c r="A27" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B27" s="12" t="s">
         <v>98</v>
@@ -19290,7 +19290,7 @@
     <row r="28">
       <c r="A28" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>270</v>
@@ -19312,7 +19312,7 @@
     <row r="29">
       <c r="A29" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B29" s="12" t="s">
         <v>203</v>
@@ -19334,7 +19334,7 @@
     <row r="30">
       <c r="A30" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B30" s="12" t="s">
         <v>100</v>
@@ -19356,7 +19356,7 @@
     <row r="31">
       <c r="A31" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B31" s="48" t="s">
         <v>480</v>
@@ -19381,7 +19381,7 @@
     <row r="32">
       <c r="A32" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>73</v>
@@ -19403,7 +19403,7 @@
     <row r="33">
       <c r="A33" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B33" s="48" t="s">
         <v>481</v>
@@ -19428,7 +19428,7 @@
     <row r="34">
       <c r="A34" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>135</v>
@@ -19450,7 +19450,7 @@
     <row r="35">
       <c r="A35" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B35" s="12" t="s">
         <v>178</v>
@@ -19472,7 +19472,7 @@
     <row r="36">
       <c r="A36" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B36" s="12" t="s">
         <v>191</v>
@@ -19494,7 +19494,7 @@
     <row r="37">
       <c r="A37" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B37" s="48" t="s">
         <v>483</v>
@@ -19519,7 +19519,7 @@
     <row r="38">
       <c r="A38" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>160</v>
@@ -19541,7 +19541,7 @@
     <row r="39">
       <c r="A39" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B39" s="12" t="s">
         <v>289</v>
@@ -19563,7 +19563,7 @@
     <row r="40">
       <c r="A40" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B40" s="12" t="s">
         <v>172</v>
@@ -19585,7 +19585,7 @@
     <row r="41">
       <c r="A41" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B41" s="12" t="s">
         <v>129</v>
@@ -19607,7 +19607,7 @@
     <row r="42">
       <c r="A42" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>105</v>
@@ -19629,7 +19629,7 @@
     <row r="43">
       <c r="A43" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B43" s="12" t="s">
         <v>114</v>
@@ -19651,7 +19651,7 @@
     <row r="44">
       <c r="A44" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B44" s="48" t="s">
         <v>484</v>
@@ -19676,7 +19676,7 @@
     <row r="45">
       <c r="A45" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B45" s="12" t="s">
         <v>236</v>
@@ -19698,7 +19698,7 @@
     <row r="46">
       <c r="A46" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B46" s="12" t="s">
         <v>252</v>
@@ -19720,7 +19720,7 @@
     <row r="47">
       <c r="A47" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B47" s="12" t="s">
         <v>92</v>
@@ -19742,7 +19742,7 @@
     <row r="48">
       <c r="A48" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>147</v>
@@ -19764,7 +19764,7 @@
     <row r="49">
       <c r="A49" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B49" s="12" t="s">
         <v>122</v>
@@ -19786,7 +19786,7 @@
     <row r="50">
       <c r="A50" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B50" s="48" t="s">
         <v>485</v>
@@ -19811,7 +19811,7 @@
     <row r="51">
       <c r="A51" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B51" s="12" t="s">
         <v>184</v>
@@ -19833,7 +19833,7 @@
     <row r="52">
       <c r="A52" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>145</v>
@@ -19855,7 +19855,7 @@
     <row r="53">
       <c r="A53" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B53" s="12" t="s">
         <v>274</v>
@@ -19877,7 +19877,7 @@
     <row r="54">
       <c r="A54" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>116</v>
@@ -19899,7 +19899,7 @@
     <row r="55">
       <c r="A55" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B55" s="48" t="s">
         <v>486</v>
@@ -19924,7 +19924,7 @@
     <row r="56">
       <c r="A56" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B56" s="12" t="s">
         <v>193</v>
@@ -19946,7 +19946,7 @@
     <row r="57">
       <c r="A57" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B57" s="12" t="s">
         <v>195</v>
@@ -19968,7 +19968,7 @@
     <row r="58">
       <c r="A58" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B58" s="48" t="s">
         <v>487</v>
@@ -19993,7 +19993,7 @@
     <row r="59">
       <c r="A59" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B59" s="12" t="s">
         <v>127</v>
@@ -20015,7 +20015,7 @@
     <row r="60">
       <c r="A60" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B60" s="12" t="s">
         <v>232</v>
@@ -20037,7 +20037,7 @@
     <row r="61">
       <c r="A61" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B61" s="48" t="s">
         <v>488</v>
@@ -20062,7 +20062,7 @@
     <row r="62">
       <c r="A62" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>189</v>
@@ -20084,7 +20084,7 @@
     <row r="63">
       <c r="A63" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B63" s="12" t="s">
         <v>212</v>
@@ -20106,7 +20106,7 @@
     <row r="64">
       <c r="A64" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>120</v>
@@ -20128,7 +20128,7 @@
     <row r="65">
       <c r="A65" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B65" s="12" t="s">
         <v>248</v>
@@ -20150,7 +20150,7 @@
     <row r="66">
       <c r="A66" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B66" s="48" t="s">
         <v>489</v>
@@ -20175,7 +20175,7 @@
     <row r="67">
       <c r="A67" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B67" s="12" t="s">
         <v>260</v>
@@ -20197,7 +20197,7 @@
     <row r="68">
       <c r="A68" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>220</v>
@@ -20219,7 +20219,7 @@
     <row r="69">
       <c r="A69" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B69" s="12" t="s">
         <v>268</v>
@@ -20241,7 +20241,7 @@
     <row r="70">
       <c r="A70" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B70" s="12" t="s">
         <v>124</v>
@@ -20263,7 +20263,7 @@
     <row r="71">
       <c r="A71" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B71" s="48" t="s">
         <v>490</v>
@@ -20288,7 +20288,7 @@
     <row r="72">
       <c r="A72" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>131</v>
@@ -20310,7 +20310,7 @@
     <row r="73">
       <c r="A73" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B73" s="12" t="s">
         <v>201</v>
@@ -20332,7 +20332,7 @@
     <row r="74">
       <c r="A74" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>262</v>
@@ -20354,7 +20354,7 @@
     <row r="75">
       <c r="A75" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B75" s="48" t="s">
         <v>491</v>
@@ -20379,7 +20379,7 @@
     <row r="76">
       <c r="A76" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B76" s="12" t="s">
         <v>110</v>
@@ -20401,7 +20401,7 @@
     <row r="77">
       <c r="A77" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B77" s="12" t="s">
         <v>141</v>
@@ -20423,7 +20423,7 @@
     <row r="78">
       <c r="A78" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B78" s="48" t="s">
         <v>492</v>
@@ -20448,7 +20448,7 @@
     <row r="79">
       <c r="A79" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B79" s="12" t="s">
         <v>228</v>
@@ -20470,7 +20470,7 @@
     <row r="80">
       <c r="A80" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B80" s="12" t="s">
         <v>118</v>
@@ -20492,7 +20492,7 @@
     <row r="81">
       <c r="A81" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B81" s="12" t="s">
         <v>234</v>
@@ -20514,7 +20514,7 @@
     <row r="82">
       <c r="A82" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>187</v>
@@ -20536,7 +20536,7 @@
     <row r="83">
       <c r="A83" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B83" s="48" t="s">
         <v>493</v>
@@ -20558,7 +20558,7 @@
     <row r="84">
       <c r="A84" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>230</v>
@@ -20580,7 +20580,7 @@
     <row r="85">
       <c r="A85" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B85" s="12" t="s">
         <v>137</v>
@@ -20602,7 +20602,7 @@
     <row r="86">
       <c r="A86" s="19" t="str">
         <f t="shared" si="1"/>
-        <v>Loading...</v>
+        <v>#NAME?</v>
       </c>
       <c r="B86" s="48" t="s">
         <v>494</v>
